--- a/results/Int All Data -1.0/Rando_6_permute.xlsx
+++ b/results/Int All Data -1.0/Rando_6_permute.xlsx
@@ -440,187 +440,187 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8941033274536878</v>
+        <v>0.8806526406525608</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8952175335818215</v>
+        <v>0.8787821950499237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8955756997709332</v>
+        <v>0.8802148598063708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8950185967068665</v>
+        <v>0.8754790846908398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.895058304267665</v>
+        <v>0.8744840012451014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.895058304267665</v>
+        <v>0.8718974227997223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8921536662649352</v>
+        <v>0.874802659408896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8921536662649352</v>
+        <v>0.8782252915213383</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8857066748609237</v>
+        <v>0.8788620092424835</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8791004541427556</v>
+        <v>0.880533318434684</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8798167865209792</v>
+        <v>0.880095537588494</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8802138621289637</v>
+        <v>0.8783047066429353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8778659281193382</v>
+        <v>0.8779465404538235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8743243728599819</v>
+        <v>0.8788221021462036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8763540477767756</v>
+        <v>0.8844332394186334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8762744331196973</v>
+        <v>0.880851577527516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8739664062063516</v>
+        <v>0.882284242283963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8731704591710499</v>
+        <v>0.8780658626717003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8751602269915637</v>
+        <v>0.887258861370729</v>
       </c>
     </row>
     <row r="21">
@@ -630,1357 +630,1357 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8666442521809228</v>
+        <v>0.8886119114700977</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8582072934209161</v>
+        <v>0.8824432720626382</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8540683289302504</v>
+        <v>0.8856667677646439</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8517603020169047</v>
+        <v>0.8863831001428675</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8517603020169047</v>
+        <v>0.8884524826204596</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8523174050809714</v>
+        <v>0.89016369890894</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8556602230008541</v>
+        <v>0.9101810984029179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8527152788308817</v>
+        <v>0.9101810984029179</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.856615199814831</v>
+        <v>0.9058427979663344</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8518792251638186</v>
+        <v>0.9058427979663344</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8479393970835893</v>
+        <v>0.9087478350400268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8471037424874891</v>
+        <v>0.8980824640237528</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8662852878498855</v>
+        <v>0.8983610155557862</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8658874140999753</v>
+        <v>0.8980822644882713</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8662455802890869</v>
+        <v>0.8943014661867174</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8678374743596906</v>
+        <v>0.8949381839078625</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8713794286900096</v>
+        <v>0.8992361781772034</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8713794286900096</v>
+        <v>0.8750401066317612</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8739662066708702</v>
+        <v>0.8351244303262007</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.868155932988004</v>
+        <v>0.8375519789929045</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.868155932988004</v>
+        <v>0.836835646614681</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8831592053698989</v>
+        <v>0.8441581997110726</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8813683744243401</v>
+        <v>0.8502470249259724</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8849899434117374</v>
+        <v>0.8579676513077555</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8849899434117374</v>
+        <v>0.8475012171664364</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8777470049724242</v>
+        <v>0.8763532496348501</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.869946963469044</v>
+        <v>0.8736072423398329</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8706632958472675</v>
+        <v>0.8761940203206935</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8713399206646926</v>
+        <v>0.8649715462403524</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8716188712676889</v>
+        <v>0.8676379388782913</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8740464199343927</v>
+        <v>0.8676379388782913</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8709823530820251</v>
+        <v>0.8689512814168616</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.873011628927856</v>
+        <v>0.8689512814168616</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8601974603123927</v>
+        <v>0.8657277857148558</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8437242100390292</v>
+        <v>0.8657277857148558</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.842489883551093</v>
+        <v>0.7872494832031032</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8516036666640062</v>
+        <v>0.7792902123855664</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8578511225866183</v>
+        <v>0.7815188241773152</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8581296741186517</v>
+        <v>0.7825137080875721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8594029100254608</v>
+        <v>0.7866129650174394</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8598807975034121</v>
+        <v>0.8137148717784997</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8436851010846749</v>
+        <v>0.8137148717784997</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8488979655362316</v>
+        <v>0.8038053411657662</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8682768514897319</v>
+        <v>0.8092173420277593</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8704655561852008</v>
+        <v>0.8093364647101547</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8718186062845695</v>
+        <v>0.8021731409279198</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8666847578836469</v>
+        <v>0.7969995849661986</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8678390706435418</v>
+        <v>0.7832300404657957</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8567766240192831</v>
+        <v>0.7722065032604097</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8581284769057633</v>
+        <v>0.781120950427405</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8481794382677128</v>
+        <v>0.7802453887350249</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8548251670111979</v>
+        <v>0.7622177570615607</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8504479571557415</v>
+        <v>0.7610237367408672</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8519600370337854</v>
+        <v>0.7535022467695205</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8500103758450328</v>
+        <v>0.7482093685899227</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8438421355085362</v>
+        <v>0.7500798141925598</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8241060810433312</v>
+        <v>0.7559297954362245</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8192515823163675</v>
+        <v>0.7758677798086056</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8182568979415921</v>
+        <v>0.7637298369396046</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8200078217908708</v>
+        <v>0.7637298369396046</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.819888499572994</v>
+        <v>0.7856575891324995</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8229126593290819</v>
+        <v>0.7737584902347335</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7971222992872593</v>
+        <v>0.7667941033274537</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7940580328994102</v>
+        <v>0.7667941033274537</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7618655769368909</v>
+        <v>0.7604267265805206</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7604728192767238</v>
+        <v>0.75827772944585</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7633379492541363</v>
+        <v>0.7474134215546209</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.759439025947594</v>
+        <v>0.7292271591734442</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7524732422919443</v>
+        <v>0.7219445131733325</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7564525783974907</v>
+        <v>0.7160947314651491</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7667994907854515</v>
+        <v>0.7176469179749543</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7665205401824553</v>
+        <v>0.6793628433007958</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7665205401824553</v>
+        <v>0.6916600154839534</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7665205401824553</v>
+        <v>0.6945253449968474</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7629370824720052</v>
+        <v>0.6711649280475054</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7663978258613946</v>
+        <v>0.6722394266148406</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.763452682155941</v>
+        <v>0.656320884979767</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7674320182614873</v>
+        <v>0.6539729509701415</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7693022643286429</v>
+        <v>0.6550474495374767</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7596321762935885</v>
+        <v>0.6513065583322026</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7578413453480297</v>
+        <v>0.6517046316175943</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7570451987772466</v>
+        <v>0.6482422919443536</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7498018612669706</v>
+        <v>0.5672167194770574</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7545775434787814</v>
+        <v>0.5869561660454462</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7496035229984596</v>
+        <v>0.5858020528210327</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7492453568093478</v>
+        <v>0.5719528936635513</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7489668052773144</v>
+        <v>0.5816636869368111</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7202734035166134</v>
+        <v>0.5803505439337223</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7149009106799371</v>
+        <v>0.5869166580201292</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7134682459234901</v>
+        <v>0.5672568261088187</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.699499764548132</v>
+        <v>0.5637547788747795</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6936495837689858</v>
+        <v>0.563038446496556</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6906250249419352</v>
+        <v>0.5501045565922532</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6885947514186973</v>
+        <v>0.5494275327038654</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6967930657429504</v>
+        <v>0.5525317061879944</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5754936507809819</v>
+        <v>0.5518949884668491</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5636344589794957</v>
+        <v>0.5518949884668491</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5596547238029866</v>
+        <v>0.5248728958983486</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5596547238029866</v>
+        <v>0.5447312656136515</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5592965576138749</v>
+        <v>0.5505417388319991</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5675343799634451</v>
+        <v>0.5501835726428874</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5781999505152007</v>
+        <v>0.5511385494568644</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5684895563129035</v>
+        <v>0.5893432090094261</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5605699930561653</v>
+        <v>0.5912140536830259</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5774038039444174</v>
+        <v>0.586916059413685</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5763293053770822</v>
+        <v>0.5834140121796458</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5161970931671069</v>
+        <v>0.5799115658746439</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5161970931671069</v>
+        <v>0.5784789011181969</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5154011461318052</v>
+        <v>0.5593767708773973</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5200573065902578</v>
+        <v>0.5596551228739495</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5021489971346705</v>
+        <v>0.560331548155893</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.5667009202576403</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.529134574710075</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.5206185998994342</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.5208175367743892</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.4656617394705126</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5025071633237822</v>
+        <v>0.4671738193485566</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5040194427373076</v>
+        <v>0.4916061409039756</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5025867779808606</v>
+        <v>0.4883036291513357</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5003198553766831</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5012351246298616</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5048165869854978</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4994061824073557</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5007163323782235</v>
+        <v>0.4994061824073557</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4971372644483643</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4978527986846621</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.4956241868929133</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4941520141111493</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4995233097349371</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4995233097349371</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4995233097349371</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5006770238883879</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.5006770238883879</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.5019105522343983</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5014727713882082</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5021891037664318</v>
       </c>
     </row>
   </sheetData>
